--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/alexandra_veizu_uipath_com/Documents/Documents/Projects/REFrameworkNET5/StudioTemplates/REFramework/contentFiles/any/any/pt2/VisualBasic/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akhileshk3\Documents\UiPath\RoboticEnterpriseFramework2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00D541BD-CB78-4D75-8532-9AD73E8C785E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8C54E24-BA5C-4BF9-8DAB-2778512EC11B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6722F26-F588-418F-B864-FA3E7F548C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
     <sheet name="Constants" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="3" r:id="rId3"/>
+    <sheet name="Mail" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -160,13 +161,179 @@
   </si>
   <si>
     <t>ProcessABCQueue</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>ReceiverEmailId</t>
+  </si>
+  <si>
+    <t>SenderCredsAssetName</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>JiraHomePageNotFound</t>
+  </si>
+  <si>
+    <t>Packing Slip Printed-System Exception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,                                                       
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: There is a system exception while processing Packing Slip Printed Process. 
+Error Details :Unable to load Jira Application.Please refer to the attachment.      
+ Action: This is a system issue and needs to be looked into thoroughly. As this is something outside the control of RPA team we might take time to get this resolved. The Automation team will revert to you on this. No action is required from your side. In case of criticality please write to the RPA team or process the requests manually.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.       </t>
+  </si>
+  <si>
+    <t>PackingSlipPrinted_EmailReceivers</t>
+  </si>
+  <si>
+    <t>BotEmailId_Sender</t>
+  </si>
+  <si>
+    <t>MaxRetriedCompleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: System Exception.
+Error Details : BOT encountered an error with System Exception. Please refer to the attachment.      
+Action: This is a system issue and needs to be looked into thoroughly. As this is something outside the control of RPA team we might take time to get this resolved. The Automation team will revert to you on this. No action is required from your side. In case of criticality please write to the RPA team or process the requests manually.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                        </t>
+  </si>
+  <si>
+    <t>InvalidJiraCreds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: System Exception 
+Error Details : BOT encountered an error Due to Invalid Credentials . Please refer to the attachment.      
+Action: This is a system issue and needs to be looked into thoroughly. As this is something outside the control of RPA team we might take time to get this resolved. The Automation team will revert to you on this. No action is required from your side. In case of criticality please write to the RPA team or process the requests manually.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                        </t>
+  </si>
+  <si>
+    <t>NoTicketData</t>
+  </si>
+  <si>
+    <t>Packing Slip Printed-Business Exception</t>
+  </si>
+  <si>
+    <t>Dear Team,
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: Business Exception 
+Error Details : There was no valid data in Jira to process further.
+Action: Please correct the data present in Jira ticket.
+Regards,
+RPA Bot                                                                                                              
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Packing Slip Printed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has successfully run on the production environment
+ No tickets are available on Jira queue to process.
+ Action: No action is needed from your end.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                        </t>
+  </si>
+  <si>
+    <t>TicketData</t>
+  </si>
+  <si>
+    <t>Packing Slip Printed: Jira Tickets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has successfully extracted the data from Jira on the production environment. Please refer to the attachment.
+Action: No action is needed from your end.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                        </t>
+  </si>
+  <si>
+    <t>Faileddata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: Business Exception 
+Error Details: Please refer to the attachment. Bot was unable to process due to exception
+Action: Bot was unable to process due to business exception and we request you to please correct relevant information from your end. BOT will be picking up the error items in the next run. In case of urgency we request you to please perform the task manually. 
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                        </t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: There is a system exception while checking if user exists in JDE. 
+Error Details : Please refer to the attachment, {1}            
+Action: This is a system issue and needs to be looked into thoroughly. As this is something outside the control of RPA team we might take time to get this resolved. The Automation team will revert to you on this. No action is required from your side. In case of criticality please write to the RPA team or process the requests manually.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+  </si>
+  <si>
+    <t>ApiError</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has faulted on the production environment
+Reason of failure: Error while creating Jira Ticket throuh API.             
+Action: This is a system issue and needs to be looked into thoroughly. As this is something outside the control of RPA team we might take time to get this resolved. The Automation team will revert to you on this. No action is required from your side. In case of criticality please write to the RPA team or process the requests manually.
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Packing Slip Printed Ticket Created- {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dear Team,
+This is to notify you that the Packing Slip Printed process has been successfully completed on the production environment. Please refer to the attachment and find the Ticket Number below that has been created by bot.
+ Ticket Number-{0}     
+Regards,
+RPA Bot                                                                                                                                                                                                                
+Disclaimer: You have received this mail because you are registered to the automated emails for the RPA process. This is a system generated email, please do not reply to this email. In case of any queries or suggestions please write to WB-USA-RPAAMSTeam@nov.com or we recommend you to contact the RPA team.                        </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -190,6 +357,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF4E5E65"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF464E55"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -211,22 +390,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E8916CA0-A30D-45E4-B7A9-BD1F4187B507}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -239,9 +428,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -279,7 +468,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -385,7 +574,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,7 +716,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -536,12 +725,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5546875" customWidth="1"/>
+    <col min="1" max="1" width="43.54296875" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.44140625" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="81.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -589,7 +778,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.2">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -599,7 +788,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="28.8">
+    <row r="5" spans="1:26" ht="29">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1613,12 +1802,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.44140625" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="75.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1655,7 +1844,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="28.8">
+    <row r="2" spans="1:26" ht="29">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1666,7 +1855,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.2">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1780,7 +1969,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="28.8">
+    <row r="17" spans="1:3" ht="29">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2771,12 +2960,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" customWidth="1"/>
-    <col min="3" max="3" width="60.33203125" customWidth="1"/>
-    <col min="4" max="26" width="65.44140625" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" customWidth="1"/>
+    <col min="3" max="3" width="60.36328125" customWidth="1"/>
+    <col min="4" max="26" width="65.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -3818,4 +4007,221 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705AF704-E05C-4C58-A99B-8FD9C9FECD71}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="21.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.6328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.90625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>